--- a/transportation_incident_forms/027_navigation_records_and_evidence_form--transportation_incident_forms.xlsx
+++ b/transportation_incident_forms/027_navigation_records_and_evidence_form--transportation_incident_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'incident',_'label':_'incident'}</t>
+          <t>incident</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Incident', 'label': 'Incident'}</t>
+          <t>Incident</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'event',_'label':_'event'}</t>
+          <t>event</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Event', 'label': 'Event'}</t>
+          <t>Event</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'observation',_'label':_'observation'}</t>
+          <t>observation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Observation', 'label': 'Observation'}</t>
+          <t>Observation</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'navigation-records-and-evidence-form-page-4-option-1',_'label':_'navigation-records-and-evidence-form-page-4-option-1'}</t>
+          <t>navigation-records-and-evidence-form-page-4-option-1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'navigation-records-and-evidence-form-page-4-option-1', 'label': 'navigation-records-and-evidence-form-page-4-option-1'}</t>
+          <t>navigation-records-and-evidence-form-page-4-option-1</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'navigation-records-and-evidence-form-page-4-option-2',_'label':_'navigation-records-and-evidence-form-page-4-option-2'}</t>
+          <t>navigation-records-and-evidence-form-page-4-option-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'navigation-records-and-evidence-form-page-4-option-2', 'label': 'navigation-records-and-evidence-form-page-4-option-2'}</t>
+          <t>navigation-records-and-evidence-form-page-4-option-2</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'navigation-records-and-evidence-form-page-9-option-1',_'label':_'navigation-records-and-evidence-form-page-9-option-1'}</t>
+          <t>navigation-records-and-evidence-form-page-9-option-1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'navigation-records-and-evidence-form-page-9-option-1', 'label': 'navigation-records-and-evidence-form-page-9-option-1'}</t>
+          <t>navigation-records-and-evidence-form-page-9-option-1</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'navigation-records-and-evidence-form-page-9-option-2',_'label':_'navigation-records-and-evidence-form-page-9-option-2'}</t>
+          <t>navigation-records-and-evidence-form-page-9-option-2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'navigation-records-and-evidence-form-page-9-option-2', 'label': 'navigation-records-and-evidence-form-page-9-option-2'}</t>
+          <t>navigation-records-and-evidence-form-page-9-option-2</t>
         </is>
       </c>
     </row>
